--- a/test_automation/IT23288058_Test_Cases.xlsx
+++ b/test_automation/IT23288058_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dushan Rathnayake\Desktop\IT23288058\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A26FFC-9EBA-42C3-A185-240E9B15A860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B388CE1-E563-42EB-B26F-2B3088DE13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="176">
   <si>
     <t>Neg ID</t>
   </si>
@@ -37,12 +37,6 @@
     <t>Singlish Input Type Covered</t>
   </si>
   <si>
-    <t>Actual output</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>Neg001</t>
   </si>
   <si>
@@ -58,12 +52,6 @@
     <t>1) Question forms</t>
   </si>
   <si>
-    <t>මොනවද මෙය කරන්නේ?</t>
-  </si>
-  <si>
-    <t>UI Error</t>
-  </si>
-  <si>
     <t>Neg002</t>
   </si>
   <si>
@@ -73,12 +61,6 @@
     <t>ඔයාගේ අයියාට කොහොමද?</t>
   </si>
   <si>
-    <t>ඔයාගෙ අයියට කොහොමද?</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
     <t>Neg003</t>
   </si>
   <si>
@@ -91,9 +73,6 @@
     <t>2) Command forms</t>
   </si>
   <si>
-    <t>මට ඒක එවන්න, please.</t>
-  </si>
-  <si>
     <t>Neg004</t>
   </si>
   <si>
@@ -103,9 +82,6 @@
     <t>PIN එක දන්නවද?</t>
   </si>
   <si>
-    <t>PIN ඒක දන්නවද?</t>
-  </si>
-  <si>
     <t>Neg005</t>
   </si>
   <si>
@@ -118,9 +94,6 @@
     <t>3) Greetings</t>
   </si>
   <si>
-    <t>සුබ දවසක්! ඔබව ගවුරවයෙන් පිළිගන්නවා අපේ මාතෘ බූමියට!</t>
-  </si>
-  <si>
     <t>Neg006</t>
   </si>
   <si>
@@ -133,9 +106,6 @@
     <t>සුබ නත්තලක් වේවා!</t>
   </si>
   <si>
-    <t>සුබ නට්ටලක් වේවා!</t>
-  </si>
-  <si>
     <t>Neg007</t>
   </si>
   <si>
@@ -148,9 +118,6 @@
     <t>4) Requests</t>
   </si>
   <si>
-    <t>පුලුවන්නම් මට උදව්වක් කරන්න කියලා කරුණාකරලා බලන්න.</t>
-  </si>
-  <si>
     <t>Neg008</t>
   </si>
   <si>
@@ -163,9 +130,6 @@
     <t>7) Punctuation Marks</t>
   </si>
   <si>
-    <t>ඔයා එනවද... නත්ත?</t>
-  </si>
-  <si>
     <t>Neg009</t>
   </si>
   <si>
@@ -178,9 +142,6 @@
     <t>9) English Word Insertions</t>
   </si>
   <si>
-    <t>බස් එක තවම ආවේ නෑ.</t>
-  </si>
-  <si>
     <t>Neg010</t>
   </si>
   <si>
@@ -193,9 +154,6 @@
     <t>11) Digital Terms</t>
   </si>
   <si>
-    <t>Router එක restart කරන්න.</t>
-  </si>
-  <si>
     <t>Neg011</t>
   </si>
   <si>
@@ -208,9 +166,6 @@
     <t>6) Repeated Words</t>
   </si>
   <si>
-    <t>අයියෝ අයියෝ, මොකෝ වුනේ?</t>
-  </si>
-  <si>
     <t>Neg012</t>
   </si>
   <si>
@@ -220,9 +175,6 @@
     <t>Login details මතක නෑ.</t>
   </si>
   <si>
-    <t>login details මතක නෑ.</t>
-  </si>
-  <si>
     <t>Neg013</t>
   </si>
   <si>
@@ -235,9 +187,6 @@
     <t>Mixed (Any)</t>
   </si>
   <si>
-    <t>අද මම Kandy ගිහිල්ලා Colombo එන්න හිතන් ඉන්නේ bus එකෙන්, ඒත් ගොඩක් තඩි rain එකක් තියෙනවා කියලා කට්ටිය කියනවා නිසා මම ආයෙත් හිතලා බලන්න ඕනේ මේක කරන්න පුළුවන්ද කියලා.</t>
-  </si>
-  <si>
     <t>Neg014</t>
   </si>
   <si>
@@ -247,9 +196,6 @@
     <t>ෆෝන් එක charge කරනවා, battery dead.</t>
   </si>
   <si>
-    <t>phone එක charge කරනවා, battery dead.</t>
-  </si>
-  <si>
     <t>Neg015</t>
   </si>
   <si>
@@ -259,9 +205,6 @@
     <t>අපි Kandy side trip එකක් යනවද next week?</t>
   </si>
   <si>
-    <t>PASS</t>
-  </si>
-  <si>
     <t>Neg016</t>
   </si>
   <si>
@@ -283,9 +226,6 @@
     <t>මම අද දිවා ආහාරය සඳහා පිටතට යන්නද?</t>
   </si>
   <si>
-    <t>මම අද lunch එකට එලියට යන්නද?</t>
-  </si>
-  <si>
     <t>Neg018</t>
   </si>
   <si>
@@ -295,9 +235,6 @@
     <t>මම ක්‍රීඩාව කිරීමට උත්සාහ කරන විට විදුලිය විසන්ධි විය.</t>
   </si>
   <si>
-    <t>මම game එක play කරන්න try කරනකොට power cut වුණා.</t>
-  </si>
-  <si>
     <t>Neg019</t>
   </si>
   <si>
@@ -307,9 +244,6 @@
     <t>ඔයා සුබ උදෑසනක් කියන එක බොහොම හොඳයි, දිගටම කරගෙන යන්න!</t>
   </si>
   <si>
-    <t>ඔයා good morning කියන්න බොහොම හොඳයි, keep it up!</t>
-  </si>
-  <si>
     <t>Neg020</t>
   </si>
   <si>
@@ -325,9 +259,6 @@
     <t>ඔයා data on කරන්න.</t>
   </si>
   <si>
-    <t>ඔය data on කරන්න.</t>
-  </si>
-  <si>
     <t>Neg022</t>
   </si>
   <si>
@@ -337,9 +268,6 @@
     <t>විශ්වවිද්‍යාලයේ විෂය හෙට තියෙනවා, මම ගියොත් හරිද?</t>
   </si>
   <si>
-    <t>uni එකේ sub එක හෙට තියෙනවා, මම ගියොත් ඕක වැඩ්?</t>
-  </si>
-  <si>
     <t>Neg023</t>
   </si>
   <si>
@@ -352,9 +280,6 @@
     <t>12) Platform/App Names</t>
   </si>
   <si>
-    <t>මම මේක Facebook ඒකට දැම්මා.</t>
-  </si>
-  <si>
     <t>Neg024</t>
   </si>
   <si>
@@ -364,9 +289,6 @@
     <t>හෙට වෛද්‍යවරයකු හමුවීමට යා යුතුය.</t>
   </si>
   <si>
-    <t>හෙට doc එකක් දිහා යන්න ඕනේ.</t>
-  </si>
-  <si>
     <t>Neg025</t>
   </si>
   <si>
@@ -376,9 +298,6 @@
     <t>අපි සතියේ කොළඹ 7 ගිහින් කඩයකට ගියා.</t>
   </si>
   <si>
-    <t>අපි සතියේ Colombo 7 වලට ගිහිල්ලා ෂොප් එකක් දිහා ගියා.</t>
-  </si>
-  <si>
     <t>Neg026</t>
   </si>
   <si>
@@ -391,9 +310,6 @@
     <t>13) Abbreviations</t>
   </si>
   <si>
-    <t>මම SLT ඒකෙන් කතා කරන්නෙ.</t>
-  </si>
-  <si>
     <t>Neg027</t>
   </si>
   <si>
@@ -406,9 +322,6 @@
     <t>14) English Clipped Forms</t>
   </si>
   <si>
-    <t>මම මාත් class එකට යනවා.</t>
-  </si>
-  <si>
     <t>Neg028</t>
   </si>
   <si>
@@ -418,9 +331,6 @@
     <t>Lab repo එක බලන්න.</t>
   </si>
   <si>
-    <t>ලබ්‍රෙපෝ එක බලන්න.</t>
-  </si>
-  <si>
     <t>Neg029</t>
   </si>
   <si>
@@ -433,9 +343,6 @@
     <t>15) Place Names</t>
   </si>
   <si>
-    <t>ගාල්ලේ ගිය දවසේ මතකයි.</t>
-  </si>
-  <si>
     <t>Neg030</t>
   </si>
   <si>
@@ -445,9 +352,6 @@
     <t>කවිඳු මචන් බෝලයත් එක්ක එනවා ක්‍රීඩාවක් කරන්න, ඔයා එනවාද?</t>
   </si>
   <si>
-    <t>කාවින්ද මචං බල්ලත් එනවා ගමේ එකක් ගහන්න, ඔයා එනවද?</t>
-  </si>
-  <si>
     <t>Neg031</t>
   </si>
   <si>
@@ -457,9 +361,6 @@
     <t>දුම්රිය පෙ.ව. 6:45 ට පිටත් වෙනවා, ඔයා එන්න ඕනේ නම් පෙ.ව. 6:30 ට එන්න.</t>
   </si>
   <si>
-    <t>train එක 6:45ට පිටත් වෙනවා, ඔයා එන්න ඕන නම් 6:30ට එන්න.</t>
-  </si>
-  <si>
     <t>Neg032</t>
   </si>
   <si>
@@ -472,9 +373,6 @@
     <t>16) Person Names</t>
   </si>
   <si>
-    <t>නිමලාට දෙන්න එක.</t>
-  </si>
-  <si>
     <t>Neg033</t>
   </si>
   <si>
@@ -487,9 +385,6 @@
     <t>17) Numbers/Suffixes</t>
   </si>
   <si>
-    <t>ළමයි 5 දෙනෙක් අවිත් හිටියා.</t>
-  </si>
-  <si>
     <t>Neg034</t>
   </si>
   <si>
@@ -499,9 +394,6 @@
     <t>ඊළඟ සම්මුඛ පරීක්ෂණය මාර්තු 20 වැනිදාට නියම කරන්නම් කියලා කිව්වා.</t>
   </si>
   <si>
-    <t>ඊළඟ interview එක මාර්තු 20 ට fix කරන්නම් කියලා කිව්වා.</t>
-  </si>
-  <si>
     <t>Neg035</t>
   </si>
   <si>
@@ -511,9 +403,6 @@
     <t>මම 2025-12-31 දිනට ගිවිසුම අවසන් කරමු කියලා කිව්වා.</t>
   </si>
   <si>
-    <t>මම 2025-12-31 වලට contract එක නවත්තමු කියලා කිව්වා.</t>
-  </si>
-  <si>
     <t>Neg036</t>
   </si>
   <si>
@@ -523,9 +412,6 @@
     <t>ඒ බෑග් එක කිලෝග්‍රෑම් 5 ක් විතර දාන්න, කොහොම හරි යනවා නම්.</t>
   </si>
   <si>
-    <t>ඒ bag එක kg 5ක් විතර දාන්න, කොහොම හරි යනවා නුම්.</t>
-  </si>
-  <si>
     <t>Neg037</t>
   </si>
   <si>
@@ -535,9 +421,6 @@
     <t>ඒ බිත්තියේ පහළ අඩි 6 ක් විතර තියෙනවා, පරීක්ෂා කළාද?</t>
   </si>
   <si>
-    <t>ඒ wall එකේ පහල අට feet 6ක් විතර තියෙනවා, check කරාද?</t>
-  </si>
-  <si>
     <t>Neg038</t>
   </si>
   <si>
@@ -556,12 +439,6 @@
     <t>Neg040</t>
   </si>
   <si>
-    <t>March masaye niwaduwa thiyenne.</t>
-  </si>
-  <si>
-    <t>මාර්තු මාසයේ නිවාඩුව තියෙන්නේ.</t>
-  </si>
-  <si>
     <t>Neg041</t>
   </si>
   <si>
@@ -574,9 +451,6 @@
     <t>21) Measurements</t>
   </si>
   <si>
-    <t>ලිටර් 2ක් දෙන්න මට.</t>
-  </si>
-  <si>
     <t>Neg042</t>
   </si>
   <si>
@@ -586,9 +460,6 @@
     <t>මීටර් 50ක් විතර තියෙනවා.</t>
   </si>
   <si>
-    <t>meter 50ක් විතර තියෙනවා.</t>
-  </si>
-  <si>
     <t>Neg043</t>
   </si>
   <si>
@@ -601,9 +472,6 @@
     <t>22) Slang/Casual</t>
   </si>
   <si>
-    <t>අඩෝ, මොකෝ වෙන්නේ බං?</t>
-  </si>
-  <si>
     <t>Neg044</t>
   </si>
   <si>
@@ -613,9 +481,6 @@
     <t>සුපිරියටම වැඩේ තියෙනවා.</t>
   </si>
   <si>
-    <t>සුපිරියටම වඩේ තියෙනවා.</t>
-  </si>
-  <si>
     <t>Neg045</t>
   </si>
   <si>
@@ -640,12 +505,6 @@
     <t>Neg047</t>
   </si>
   <si>
-    <t>Mage hina yanawa 😂.</t>
-  </si>
-  <si>
-    <t>මගේ හිනා යනවා 😂.</t>
-  </si>
-  <si>
     <t>24) Emojis</t>
   </si>
   <si>
@@ -658,9 +517,6 @@
     <t>දුකෙන් ඉන්නේ 😢.</t>
   </si>
   <si>
-    <t>දුකෙන් ඉන්නේ.</t>
-  </si>
-  <si>
     <t>Neg049</t>
   </si>
   <si>
@@ -670,9 +526,6 @@
     <t>මචන් ඔයා busy නැද්ද bro? හෙට අම්මත් එක්ක ගාල්ල යමු.</t>
   </si>
   <si>
-    <t>මචන් ඔයා busy නැද්ද bro? හෙට අම්මත් එක්ක ගාල්ලේ යමු.</t>
-  </si>
-  <si>
     <t>Neg050</t>
   </si>
   <si>
@@ -682,7 +535,19 @@
     <t>අද 10pm වෙනකන් lab එකේ වැඩ කරන්න පුළුවන්ද?</t>
   </si>
   <si>
-    <t>fail</t>
+    <t>Mam happy 😊</t>
+  </si>
+  <si>
+    <t>මම happy 😊</t>
+  </si>
+  <si>
+    <t>Ado macha, ASAP enna!</t>
+  </si>
+  <si>
+    <t>අඩෝ මචං, ASAP එන්න!</t>
+  </si>
+  <si>
+    <t>Slang + mixed English abbreviation</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +887,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
@@ -1032,7 +897,7 @@
     <col min="6" max="6" width="12.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1048,1132 +913,829 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G2" t="s">
+      <c r="E3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="D6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="E7" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="3" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="1" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="F8" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="12" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="D12" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G9" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+    </row>
+    <row r="13" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F10" t="s">
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="3" t="s">
+    </row>
+    <row r="15" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="F11" t="s">
+      <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="E15" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E16" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="F12" t="s">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G12" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="3" t="s">
+      <c r="E17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="18" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="1"/>
+    </row>
+    <row r="20" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" s="1"/>
+    </row>
+    <row r="21" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" t="s">
-        <v>71</v>
-      </c>
-      <c r="G14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D21" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="G15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="E21" s="1"/>
+    </row>
+    <row r="22" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F16" t="s">
-        <v>78</v>
-      </c>
-      <c r="G16" t="s">
+      <c r="E22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E23" s="1"/>
+    </row>
+    <row r="24" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F17" t="s">
-        <v>82</v>
-      </c>
-      <c r="G17" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="D24" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="E24" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="3" t="s">
+    </row>
+    <row r="25" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="G18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="E25" s="1"/>
+    </row>
+    <row r="26" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" t="s">
+      <c r="D26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="G19" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="E26" s="1"/>
+    </row>
+    <row r="27" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D27" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" t="s">
+      <c r="E27" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+    </row>
+    <row r="28" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="1"/>
-      <c r="F21" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="1" t="s">
+      <c r="E28" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="D22" s="1" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G22" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="E29" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E23" s="1"/>
-      <c r="F23" t="s">
+      <c r="D30" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G23" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="E30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="1" t="s">
+    </row>
+    <row r="31" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F24" t="s">
+      <c r="E31" s="1"/>
+    </row>
+    <row r="32" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="G24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="D32" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="E32" s="1"/>
+    </row>
+    <row r="33" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E25" s="1"/>
-      <c r="F25" t="s">
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C33" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="G25" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="3" t="s">
+      <c r="E33" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D26" s="3" t="s">
+    </row>
+    <row r="34" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E26" s="1"/>
-      <c r="F26" t="s">
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G26" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="E34" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="D27" s="1" t="s">
+    </row>
+    <row r="35" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="B35" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F27" t="s">
+      <c r="D35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="G27" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="E35" s="1"/>
+    </row>
+    <row r="36" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="1" t="s">
+      <c r="B36" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="F28" t="s">
+      <c r="B37" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G28" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="1" t="s">
+      <c r="E37" s="1"/>
+    </row>
+    <row r="38" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="B38" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E29" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F29" t="s">
+      <c r="D38" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="G29" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
+      <c r="E38" s="1"/>
+    </row>
+    <row r="39" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="1" t="s">
+      <c r="B39" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="1"/>
+    </row>
+    <row r="40" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F30" t="s">
+      <c r="E40" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="G30" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
+    </row>
+    <row r="41" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B31" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="3" t="s">
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="D31" s="3" t="s">
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" t="s">
+      <c r="D42" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="G31" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
+      <c r="E42" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="3" t="s">
+    </row>
+    <row r="43" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="E32" s="1"/>
-      <c r="F32" t="s">
+      <c r="D43" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
+      <c r="E43" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D44" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E44" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="F33" t="s">
+    </row>
+    <row r="45" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="G33" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="B34" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="1" t="s">
+      <c r="D45" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E45" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="F34" t="s">
+      <c r="D46" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="G34" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
+      <c r="E46" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C35" s="3" t="s">
+    </row>
+    <row r="47" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="3" t="s">
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="1"/>
-      <c r="F35" t="s">
+      <c r="D47" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="G35" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
+      <c r="E47" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C36" s="3" t="s">
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D36" s="3" t="s">
+    </row>
+    <row r="49" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E36" s="1"/>
-      <c r="F36" t="s">
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G36" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
+      <c r="D49" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C37" s="3" t="s">
+      <c r="E49" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="D37" s="3" t="s">
+      <c r="B50" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E37" s="1"/>
-      <c r="F37" t="s">
+      <c r="D50" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="G37" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
+      <c r="E50" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="B51" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C51" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="D51" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E38" s="1"/>
-      <c r="F38" t="s">
-        <v>171</v>
-      </c>
-      <c r="G38" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E39" s="1"/>
-      <c r="F39" t="s">
-        <v>159</v>
-      </c>
-      <c r="G39" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F40" t="s">
-        <v>175</v>
-      </c>
-      <c r="G40" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="F41" t="s">
-        <v>179</v>
-      </c>
-      <c r="G41" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F42" t="s">
-        <v>184</v>
-      </c>
-      <c r="G42" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="F43" t="s">
-        <v>188</v>
-      </c>
-      <c r="G43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F44" t="s">
-        <v>193</v>
-      </c>
-      <c r="G44" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="F45" t="s">
-        <v>197</v>
-      </c>
-      <c r="G45" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="F46" t="s">
-        <v>200</v>
-      </c>
-      <c r="G46" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="G47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F48" t="s">
-        <v>207</v>
-      </c>
-      <c r="G48" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="F49" t="s">
-        <v>212</v>
-      </c>
-      <c r="G49" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F50" t="s">
-        <v>216</v>
-      </c>
-      <c r="G50" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>219</v>
-      </c>
       <c r="E51" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="F51" t="s">
-        <v>219</v>
-      </c>
-      <c r="G51" t="s">
-        <v>220</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/test_automation/IT23288058_Test_Cases.xlsx
+++ b/test_automation/IT23288058_Test_Cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dushan Rathnayake\Desktop\IT23288058\test_automation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B388CE1-E563-42EB-B26F-2B3088DE13A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2445EDAE-4D34-4225-8061-6A4CFB7225F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="722" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="223">
   <si>
     <t>Neg ID</t>
   </si>
@@ -37,6 +37,12 @@
     <t>Singlish Input Type Covered</t>
   </si>
   <si>
+    <t>Actual output</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
     <t>Neg001</t>
   </si>
   <si>
@@ -52,6 +58,12 @@
     <t>1) Question forms</t>
   </si>
   <si>
+    <t>මොනවද මෙය කරන්නේ?</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
     <t>Neg002</t>
   </si>
   <si>
@@ -61,6 +73,9 @@
     <t>ඔයාගේ අයියාට කොහොමද?</t>
   </si>
   <si>
+    <t>ඔයාගෙ අයියට කොහොමද?</t>
+  </si>
+  <si>
     <t>Neg003</t>
   </si>
   <si>
@@ -73,6 +88,9 @@
     <t>2) Command forms</t>
   </si>
   <si>
+    <t>මට ඒක එවන්න, please.</t>
+  </si>
+  <si>
     <t>Neg004</t>
   </si>
   <si>
@@ -82,6 +100,9 @@
     <t>PIN එක දන්නවද?</t>
   </si>
   <si>
+    <t>PIN ඒක දන්නවද?</t>
+  </si>
+  <si>
     <t>Neg005</t>
   </si>
   <si>
@@ -94,6 +115,9 @@
     <t>3) Greetings</t>
   </si>
   <si>
+    <t>සුබ දවසක්! ඔබව ගවුරවයෙන් පිළිගන්නවා අපේ මාතෘ බූමියට!</t>
+  </si>
+  <si>
     <t>Neg006</t>
   </si>
   <si>
@@ -106,6 +130,9 @@
     <t>සුබ නත්තලක් වේවා!</t>
   </si>
   <si>
+    <t>සුබ නට්ටලක් වේවා!</t>
+  </si>
+  <si>
     <t>Neg007</t>
   </si>
   <si>
@@ -118,6 +145,9 @@
     <t>4) Requests</t>
   </si>
   <si>
+    <t>පුලුවන්නම් මට උදව්වක් කරන්න කියලා කරුණාකරලා බලන්න.</t>
+  </si>
+  <si>
     <t>Neg008</t>
   </si>
   <si>
@@ -130,6 +160,9 @@
     <t>7) Punctuation Marks</t>
   </si>
   <si>
+    <t>ඔයා එනවද... නත්ත?</t>
+  </si>
+  <si>
     <t>Neg009</t>
   </si>
   <si>
@@ -142,6 +175,9 @@
     <t>9) English Word Insertions</t>
   </si>
   <si>
+    <t>බස් එක තවම ආවේ නෑ.</t>
+  </si>
+  <si>
     <t>Neg010</t>
   </si>
   <si>
@@ -154,6 +190,9 @@
     <t>11) Digital Terms</t>
   </si>
   <si>
+    <t>Router එක restart කරන්න.</t>
+  </si>
+  <si>
     <t>Neg011</t>
   </si>
   <si>
@@ -166,6 +205,9 @@
     <t>6) Repeated Words</t>
   </si>
   <si>
+    <t>අයියෝ අයියෝ, මොකෝ වුනේ?</t>
+  </si>
+  <si>
     <t>Neg012</t>
   </si>
   <si>
@@ -175,6 +217,9 @@
     <t>Login details මතක නෑ.</t>
   </si>
   <si>
+    <t>login details මතක නෑ.</t>
+  </si>
+  <si>
     <t>Neg013</t>
   </si>
   <si>
@@ -187,6 +232,9 @@
     <t>Mixed (Any)</t>
   </si>
   <si>
+    <t>UI Error</t>
+  </si>
+  <si>
     <t>Neg014</t>
   </si>
   <si>
@@ -196,27 +244,36 @@
     <t>ෆෝන් එක charge කරනවා, battery dead.</t>
   </si>
   <si>
+    <t>අද මම Kandy ගිහිල්ලා Colombo එන්න හිතන් ඉන්නේ bus එකෙන්, ඒත් ගොඩක් තඩි rain එකක් තියෙනවා කියලා කට්ටිය කියනවා නිසා මම ආයෙත් හිතලා බලන්න ඕනේ මේක කරන්න පුළුවන්ද කියලා.</t>
+  </si>
+  <si>
     <t>Neg015</t>
   </si>
   <si>
-    <t>api Kandy side trip ekak yanwada next week?</t>
-  </si>
-  <si>
-    <t>අපි Kandy side trip එකක් යනවද next week?</t>
+    <t>oyata puluwanda meka</t>
+  </si>
+  <si>
+    <t>ඔයාට පුළුවන්ද මේක</t>
+  </si>
+  <si>
+    <t>phone එක charge කරනවා, battery dead.</t>
   </si>
   <si>
     <t>Neg016</t>
   </si>
   <si>
-    <t>Api thama gei inne.</t>
-  </si>
-  <si>
-    <t>අපි තාම ගෙයි ඉන්නේ.</t>
+    <t>oyata puluwanda meka karanna kiyala mama ahanne eka hariyata</t>
+  </si>
+  <si>
+    <t>ඔයාට පුළුවන්ද මේක කරන්න කියලා මම අහන්නේ එක හරියට</t>
   </si>
   <si>
     <t>8) Spelling Variants</t>
   </si>
   <si>
+    <t>ඔයාට පුලුවන්ද මේක</t>
+  </si>
+  <si>
     <t>Neg017</t>
   </si>
   <si>
@@ -226,6 +283,9 @@
     <t>මම අද දිවා ආහාරය සඳහා පිටතට යන්නද?</t>
   </si>
   <si>
+    <t>ඔයාට පුලුවන්ද මේක කරන්න කියලා මම අහන්නේ ඒක හරියට</t>
+  </si>
+  <si>
     <t>Neg018</t>
   </si>
   <si>
@@ -235,6 +295,9 @@
     <t>මම ක්‍රීඩාව කිරීමට උත්සාහ කරන විට විදුලිය විසන්ධි විය.</t>
   </si>
   <si>
+    <t>මම game එක play කරන්න try කරනකොට power cut වුණා.</t>
+  </si>
+  <si>
     <t>Neg019</t>
   </si>
   <si>
@@ -244,6 +307,9 @@
     <t>ඔයා සුබ උදෑසනක් කියන එක බොහොම හොඳයි, දිගටම කරගෙන යන්න!</t>
   </si>
   <si>
+    <t>ඔයා good morning කියන්න බොහොම හොඳයි, keep it up!</t>
+  </si>
+  <si>
     <t>Neg020</t>
   </si>
   <si>
@@ -259,6 +325,9 @@
     <t>ඔයා data on කරන්න.</t>
   </si>
   <si>
+    <t>ඔය data on කරන්න.</t>
+  </si>
+  <si>
     <t>Neg022</t>
   </si>
   <si>
@@ -268,6 +337,9 @@
     <t>විශ්වවිද්‍යාලයේ විෂය හෙට තියෙනවා, මම ගියොත් හරිද?</t>
   </si>
   <si>
+    <t>uni එකේ sub එක හෙට තියෙනවා, මම ගියොත් ඕක වැඩ්?</t>
+  </si>
+  <si>
     <t>Neg023</t>
   </si>
   <si>
@@ -280,6 +352,9 @@
     <t>12) Platform/App Names</t>
   </si>
   <si>
+    <t>මම මේක Facebook ඒකට දැම්මා.</t>
+  </si>
+  <si>
     <t>Neg024</t>
   </si>
   <si>
@@ -289,6 +364,9 @@
     <t>හෙට වෛද්‍යවරයකු හමුවීමට යා යුතුය.</t>
   </si>
   <si>
+    <t>හෙට doc එකක් දිහා යන්න ඕනේ.</t>
+  </si>
+  <si>
     <t>Neg025</t>
   </si>
   <si>
@@ -298,6 +376,9 @@
     <t>අපි සතියේ කොළඹ 7 ගිහින් කඩයකට ගියා.</t>
   </si>
   <si>
+    <t>අපි සතියේ Colombo 7 වලට ගිහිල්ලා ෂොප් එකක් දිහා ගියා.</t>
+  </si>
+  <si>
     <t>Neg026</t>
   </si>
   <si>
@@ -310,6 +391,9 @@
     <t>13) Abbreviations</t>
   </si>
   <si>
+    <t>මම SLT ඒකෙන් කතා කරන්නෙ.</t>
+  </si>
+  <si>
     <t>Neg027</t>
   </si>
   <si>
@@ -322,6 +406,9 @@
     <t>14) English Clipped Forms</t>
   </si>
   <si>
+    <t>මම මාත් class එකට යනවා.</t>
+  </si>
+  <si>
     <t>Neg028</t>
   </si>
   <si>
@@ -331,6 +418,9 @@
     <t>Lab repo එක බලන්න.</t>
   </si>
   <si>
+    <t>ලබ්‍රෙපෝ එක බලන්න.</t>
+  </si>
+  <si>
     <t>Neg029</t>
   </si>
   <si>
@@ -343,6 +433,9 @@
     <t>15) Place Names</t>
   </si>
   <si>
+    <t>ගාල්ලේ ගිය දවසේ මතකයි.</t>
+  </si>
+  <si>
     <t>Neg030</t>
   </si>
   <si>
@@ -352,6 +445,9 @@
     <t>කවිඳු මචන් බෝලයත් එක්ක එනවා ක්‍රීඩාවක් කරන්න, ඔයා එනවාද?</t>
   </si>
   <si>
+    <t>කාවින්ද මචං බල්ලත් එනවා ගමේ එකක් ගහන්න, ඔයා එනවද?</t>
+  </si>
+  <si>
     <t>Neg031</t>
   </si>
   <si>
@@ -361,6 +457,9 @@
     <t>දුම්රිය පෙ.ව. 6:45 ට පිටත් වෙනවා, ඔයා එන්න ඕනේ නම් පෙ.ව. 6:30 ට එන්න.</t>
   </si>
   <si>
+    <t>train එක 6:45ට පිටත් වෙනවා, ඔයා එන්න ඕන නම් 6:30ට එන්න.</t>
+  </si>
+  <si>
     <t>Neg032</t>
   </si>
   <si>
@@ -373,6 +472,9 @@
     <t>16) Person Names</t>
   </si>
   <si>
+    <t>නිමලාට දෙන්න එක.</t>
+  </si>
+  <si>
     <t>Neg033</t>
   </si>
   <si>
@@ -385,6 +487,9 @@
     <t>17) Numbers/Suffixes</t>
   </si>
   <si>
+    <t>ළමයි 5 දෙනෙක් අවිත් හිටියා.</t>
+  </si>
+  <si>
     <t>Neg034</t>
   </si>
   <si>
@@ -394,6 +499,9 @@
     <t>ඊළඟ සම්මුඛ පරීක්ෂණය මාර්තු 20 වැනිදාට නියම කරන්නම් කියලා කිව්වා.</t>
   </si>
   <si>
+    <t>ඊළඟ interview එක මාර්තු 20 ට fix කරන්නම් කියලා කිව්වා.</t>
+  </si>
+  <si>
     <t>Neg035</t>
   </si>
   <si>
@@ -403,6 +511,9 @@
     <t>මම 2025-12-31 දිනට ගිවිසුම අවසන් කරමු කියලා කිව්වා.</t>
   </si>
   <si>
+    <t>මම 2025-12-31 වලට contract එක නවත්තමු කියලා කිව්වා.</t>
+  </si>
+  <si>
     <t>Neg036</t>
   </si>
   <si>
@@ -412,6 +523,9 @@
     <t>ඒ බෑග් එක කිලෝග්‍රෑම් 5 ක් විතර දාන්න, කොහොම හරි යනවා නම්.</t>
   </si>
   <si>
+    <t>ඒ bag එක kg 5ක් විතර දාන්න, කොහොම හරි යනවා නුම්.</t>
+  </si>
+  <si>
     <t>Neg037</t>
   </si>
   <si>
@@ -421,6 +535,9 @@
     <t>ඒ බිත්තියේ පහළ අඩි 6 ක් විතර තියෙනවා, පරීක්ෂා කළාද?</t>
   </si>
   <si>
+    <t>ඒ wall එකේ පහල අට feet 6ක් විතර තියෙනවා, check කරාද?</t>
+  </si>
+  <si>
     <t>Neg038</t>
   </si>
   <si>
@@ -436,9 +553,24 @@
     <t>20) Dates</t>
   </si>
   <si>
+    <t>PASS</t>
+  </si>
+  <si>
     <t>Neg040</t>
   </si>
   <si>
+    <t>Ado macha, ASAP enna!</t>
+  </si>
+  <si>
+    <t>අඩෝ මචං, ASAP එන්න!</t>
+  </si>
+  <si>
+    <t>Slang + mixed English abbreviation</t>
+  </si>
+  <si>
+    <t>අඩෝ මච, ASAP එන්න!</t>
+  </si>
+  <si>
     <t>Neg041</t>
   </si>
   <si>
@@ -451,6 +583,9 @@
     <t>21) Measurements</t>
   </si>
   <si>
+    <t>ලිටර් 2ක් දෙන්න මට.</t>
+  </si>
+  <si>
     <t>Neg042</t>
   </si>
   <si>
@@ -460,6 +595,9 @@
     <t>මීටර් 50ක් විතර තියෙනවා.</t>
   </si>
   <si>
+    <t>meter 50ක් විතර තියෙනවා.</t>
+  </si>
+  <si>
     <t>Neg043</t>
   </si>
   <si>
@@ -472,6 +610,9 @@
     <t>22) Slang/Casual</t>
   </si>
   <si>
+    <t>අඩෝ, මොකෝ වෙන්නේ බං?</t>
+  </si>
+  <si>
     <t>Neg044</t>
   </si>
   <si>
@@ -481,6 +622,9 @@
     <t>සුපිරියටම වැඩේ තියෙනවා.</t>
   </si>
   <si>
+    <t>සුපිරියටම වඩේ තියෙනවා.</t>
+  </si>
+  <si>
     <t>Neg045</t>
   </si>
   <si>
@@ -505,6 +649,12 @@
     <t>Neg047</t>
   </si>
   <si>
+    <t>Mamaa happy 😊</t>
+  </si>
+  <si>
+    <t>මම happy 😊</t>
+  </si>
+  <si>
     <t>24) Emojis</t>
   </si>
   <si>
@@ -517,6 +667,9 @@
     <t>දුකෙන් ඉන්නේ 😢.</t>
   </si>
   <si>
+    <t>දුකෙන් ඉන්නේ.</t>
+  </si>
+  <si>
     <t>Neg049</t>
   </si>
   <si>
@@ -526,6 +679,9 @@
     <t>මචන් ඔයා busy නැද්ද bro? හෙට අම්මත් එක්ක ගාල්ල යමු.</t>
   </si>
   <si>
+    <t>මචන් ඔයා busy නැද්ද bro? හෙට අම්මත් එක්ක ගාල්ලේ යමු.</t>
+  </si>
+  <si>
     <t>Neg050</t>
   </si>
   <si>
@@ -533,21 +689,6 @@
   </si>
   <si>
     <t>අද 10pm වෙනකන් lab එකේ වැඩ කරන්න පුළුවන්ද?</t>
-  </si>
-  <si>
-    <t>Mam happy 😊</t>
-  </si>
-  <si>
-    <t>මම happy 😊</t>
-  </si>
-  <si>
-    <t>Ado macha, ASAP enna!</t>
-  </si>
-  <si>
-    <t>අඩෝ මචං, ASAP එන්න!</t>
-  </si>
-  <si>
-    <t>Slang + mixed English abbreviation</t>
   </si>
 </sst>
 </file>
@@ -887,17 +1028,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="49.95" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.77734375" customWidth="1"/>
     <col min="3" max="3" width="38.44140625" customWidth="1"/>
-    <col min="4" max="4" width="25.33203125" customWidth="1"/>
+    <col min="4" max="4" width="88.44140625" customWidth="1"/>
     <col min="5" max="5" width="28.44140625" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="46.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -913,829 +1054,1129 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
+        <v>74</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C17" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="F17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="F18" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" t="s">
+        <v>91</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" t="s">
+        <v>95</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E21" s="1"/>
+      <c r="F21" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C19" s="3" t="s">
+      <c r="F22" t="s">
+        <v>101</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E23" s="1"/>
+      <c r="F23" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F24" t="s">
+        <v>110</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="1"/>
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F27" t="s">
+        <v>123</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F28" t="s">
+        <v>128</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F29" t="s">
+        <v>132</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F30" t="s">
+        <v>137</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" t="s">
+        <v>141</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E32" s="1"/>
+      <c r="F32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F33" t="s">
+        <v>150</v>
+      </c>
+      <c r="G33" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G34" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" t="s">
+        <v>159</v>
+      </c>
+      <c r="G35" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="E36" s="1"/>
+      <c r="F36" t="s">
+        <v>163</v>
+      </c>
+      <c r="G36" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="E37" s="1"/>
+      <c r="F37" t="s">
+        <v>167</v>
+      </c>
+      <c r="G37" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" t="s">
+        <v>171</v>
+      </c>
+      <c r="G38" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="E39" s="1"/>
+      <c r="F39" t="s">
+        <v>159</v>
+      </c>
+      <c r="G39" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F40" t="s">
+        <v>175</v>
+      </c>
+      <c r="G40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F41" t="s">
+        <v>182</v>
+      </c>
+      <c r="G41" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F42" t="s">
+        <v>187</v>
+      </c>
+      <c r="G42" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F43" t="s">
+        <v>191</v>
+      </c>
+      <c r="G43" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F44" t="s">
+        <v>196</v>
+      </c>
+      <c r="G44" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F45" t="s">
+        <v>200</v>
+      </c>
+      <c r="G45" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F46" t="s">
+        <v>203</v>
+      </c>
+      <c r="G46" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="G47" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F48" t="s">
+        <v>210</v>
+      </c>
+      <c r="G48" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G49" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E19" s="1"/>
-    </row>
-    <row r="20" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E20" s="1"/>
-    </row>
-    <row r="21" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" s="1"/>
-    </row>
-    <row r="22" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E23" s="1"/>
-    </row>
-    <row r="24" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E25" s="1"/>
-    </row>
-    <row r="26" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="1"/>
-    </row>
-    <row r="27" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="E32" s="1"/>
-    </row>
-    <row r="33" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C34" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="1"/>
-    </row>
-    <row r="36" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E36" s="1"/>
-    </row>
-    <row r="37" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E37" s="1"/>
-    </row>
-    <row r="38" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E38" s="1"/>
-    </row>
-    <row r="39" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E39" s="1"/>
-    </row>
-    <row r="40" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F50" t="s">
+        <v>219</v>
+      </c>
+      <c r="G50" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="49.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>54</v>
+        <v>69</v>
+      </c>
+      <c r="F51" t="s">
+        <v>222</v>
+      </c>
+      <c r="G51" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
